--- a/excel/distribuidora-cunza-s-a_ccc.xlsx
+++ b/excel/distribuidora-cunza-s-a_ccc.xlsx
@@ -725,16 +725,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1447</v>
+        <v>109322</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C000427654</t>
+          <t>C004245880</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C000427654 - UNOCC UNOCC ANA CARMEN</t>
+          <t>C004245880 - CHAVEZ ACHARTE GLADYS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>S17777327</t>
+          <t>S17795454</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -798,11 +798,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -824,33 +824,33 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31039</v>
+        <v>1447</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C001627931</t>
+          <t>C000427654</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C001627931 - ESPINOZA CARBAJAL RICHARD OSCAR</t>
+          <t>C000427654 - UNOCC UNOCC ANA CARMEN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>S17785729</t>
+          <t>S17777327</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,11 +914,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -940,12 +940,12 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -957,7 +957,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109322</v>
+        <v>31039</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C004245880</t>
+          <t>C001627931</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C004245880 - CHAVEZ ACHARTE GLADYS</t>
+          <t>C001627931 - ESPINOZA CARBAJAL RICHARD OSCAR</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>S17795454</t>
+          <t>S17785729</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,14 +1066,14 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81312</v>
+        <v>45847</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C004213339</t>
+          <t>C001689686</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C004213339 - VARGAS ANCASI BRENDY GERALDINE</t>
+          <t>C001689686 - GALLEGOS GUISADO CARMEN ROSA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1132,11 +1132,11 @@
         <v>46235</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>S17789357</t>
+          <t>S17749850</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1189,16 +1189,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45847</v>
+        <v>63217</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C001689686</t>
+          <t>C004049715</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C001689686 - GALLEGOS GUISADO CARMEN ROSA</t>
+          <t>C004049715 - GALICIO CAMARGO MARISOL KATHERINE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1248,11 +1248,11 @@
         <v>46235</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17749850</t>
+          <t>S17828104</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63217</v>
+        <v>81312</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C004049715</t>
+          <t>C004213339</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C004049715 - GALICIO CAMARGO MARISOL KATHERINE</t>
+          <t>C004213339 - VARGAS ANCASI BRENDY GERALDINE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,11 +1364,11 @@
         <v>46235</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17828104</t>
+          <t>S17789357</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1409,19 +1409,19 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2540</v>
+        <v>76927</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C000542472</t>
+          <t>C004175414</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C000542472 - ORMEÑO SALAS ROSA SUSANA</t>
+          <t>C004175414 - RODRIGUEZ IZAGUIRRE RAQUEL PATRICIA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1480,11 +1480,11 @@
         <v>46235</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17712076</t>
+          <t>S17811120</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76927</v>
+        <v>103929</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C004175414</t>
+          <t>C001758520</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C004175414 - RODRIGUEZ IZAGUIRRE RAQUEL PATRICIA</t>
+          <t>C001758520 - GARCIA RIOFRIO RUBY YASMINE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17811120</t>
+          <t>S17824247</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103929</v>
+        <v>2540</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C001758520</t>
+          <t>C000542472</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C001758520 - GARCIA RIOFRIO RUBY YASMINE</t>
+          <t>C000542472 - ORMEÑO SALAS ROSA SUSANA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1712,11 +1712,11 @@
         <v>46235</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17824247</t>
+          <t>S17712076</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2001,16 +2001,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97413</v>
+        <v>909</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2025,22 +2025,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C001334121</t>
+          <t>C000511760</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C001334121 - PORTILLA PALMA DE FLORES EUMELIA MARINA</t>
+          <t>C000511760 - CORREA TAMAYO CARMEN JOSEFINA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>S17594718</t>
+          <t>S17590001</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2074,11 +2074,11 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2098,23 +2098,35 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95906</v>
+        <v>29955</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2139,12 +2151,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C004239859</t>
+          <t>C001565471</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C004239859 - CONDORI LLAMOCCA CLAUDIA</t>
+          <t>C001565471 - QUISPEHUAMAN ATANACIO DELFINA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2164,11 +2176,11 @@
         <v>46235</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>S17687192</t>
+          <t>S17640417</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2178,11 +2190,11 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2191,7 +2203,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2204,7 +2216,7 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2221,16 +2233,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103579</v>
+        <v>23983</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2245,22 +2257,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C001427138</t>
+          <t>C001485270</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C001427138 - MAYTA TINCO ROCIO JUANA</t>
+          <t>C001485270 - CHUMACERO CORDOVA ADALY ISABEL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2280,11 +2292,11 @@
         <v>46235</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17601147</t>
+          <t>S17640491</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2294,11 +2306,11 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2307,7 +2319,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2318,35 +2330,23 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Poco dispuesto</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67336</v>
+        <v>40450</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C004222842</t>
+          <t>C001675831</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C004222842 - NORIEGA RONDAN ROSARIO STEFANY</t>
+          <t>C001675831 - MUÑOZ COCHAN JULIA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2396,11 +2396,11 @@
         <v>46235</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>46242</v>
+        <v>46238</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17718303</t>
+          <t>S17585967</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2410,11 +2410,11 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2436,33 +2436,33 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>909</v>
+        <v>36856</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C000511760</t>
+          <t>C001657626</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C000511760 - CORREA TAMAYO CARMEN JOSEFINA</t>
+          <t>C001657626 - MACHA LAZO VICTORIA JUANA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17590001</t>
+          <t>S17605346</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2526,11 +2526,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2547,7 +2547,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
@@ -2557,28 +2561,28 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>29955</v>
+        <v>97413</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2593,22 +2597,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C001565471</t>
+          <t>C001334121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C001565471 - QUISPEHUAMAN ATANACIO DELFINA</t>
+          <t>C001334121 - PORTILLA PALMA DE FLORES EUMELIA MARINA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2628,11 +2632,11 @@
         <v>46235</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S17640417</t>
+          <t>S17594718</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2642,11 +2646,11 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2655,7 +2659,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2666,35 +2670,23 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>23983</v>
+        <v>95906</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2709,22 +2701,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C001485270</t>
+          <t>C004239859</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C001485270 - CHUMACERO CORDOVA ADALY ISABEL</t>
+          <t>C004239859 - CONDORI LLAMOCCA CLAUDIA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2744,11 +2736,11 @@
         <v>46235</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17640491</t>
+          <t>S17687192</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2758,11 +2750,11 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2771,7 +2763,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2782,14 +2774,26 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>40450</v>
+        <v>103579</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2823,12 +2827,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001675831</t>
+          <t>C001427138</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001675831 - MUÑOZ COCHAN JULIA</t>
+          <t>C001427138 - MAYTA TINCO ROCIO JUANA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2852,7 +2856,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17585967</t>
+          <t>S17601147</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2875,7 +2879,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2888,7 +2892,7 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2905,16 +2909,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>36856</v>
+        <v>67336</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2939,12 +2943,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C001657626</t>
+          <t>C004222842</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C001657626 - MACHA LAZO VICTORIA JUANA</t>
+          <t>C004222842 - NORIEGA RONDAN ROSARIO STEFANY</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2964,11 +2968,11 @@
         <v>46235</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17605346</t>
+          <t>S17718303</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2978,11 +2982,11 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2991,7 +2995,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2999,33 +3003,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>36983</v>
+        <v>77073</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C001646326</t>
+          <t>C004174131</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C001646326 - ROMAN CONTRERAS RIZO PATRON</t>
+          <t>C004174131 - RAMOS HIDALGO SOSIMA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3084,11 +3084,11 @@
         <v>46235</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17763499</t>
+          <t>S17562603</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3134,23 +3134,23 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20231</v>
+        <v>81527</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C001409695</t>
+          <t>C004213095</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C001409695 - ACHAHUANCO ADAME YOLANDA</t>
+          <t>C004213095 - CIGUEÑAS VALIENTE NINIBETH</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17559437</t>
+          <t>S17562726</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3214,11 +3214,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3245,28 +3245,28 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>77073</v>
+        <v>108237</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C004174131</t>
+          <t>C001753917</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C004174131 - RAMOS HIDALGO SOSIMA</t>
+          <t>C001753917 - MANTILLA GOICOCHEA DE ÑONTOL MARIA SUSAN</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3316,11 +3316,11 @@
         <v>46235</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>S17562603</t>
+          <t>S17705850</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,11 +3330,11 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3356,24 +3356,24 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>81527</v>
+        <v>36983</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C004213095</t>
+          <t>C001646326</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C004213095 - CIGUEÑAS VALIENTE NINIBETH</t>
+          <t>C001646326 - ROMAN CONTRERAS RIZO PATRON</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3432,11 +3432,11 @@
         <v>46235</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17562726</t>
+          <t>S17763499</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3482,23 +3482,23 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>108237</v>
+        <v>20231</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C001753917</t>
+          <t>C001409695</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C001753917 - MANTILLA GOICOCHEA DE ÑONTOL MARIA SUSAN</t>
+          <t>C001409695 - ACHAHUANCO ADAME YOLANDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3548,11 +3548,11 @@
         <v>46235</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>S17705850</t>
+          <t>S17559437</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3562,11 +3562,11 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3588,7 +3588,7 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3605,16 +3605,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>108526</v>
+        <v>3300</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3629,22 +3629,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C001670096</t>
+          <t>C000505145</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C001670096 - GROUP ONE SAC</t>
+          <t>C000505145 - ROJAS CONDO FORTUNATA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17661584</t>
+          <t>S17656685</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3678,11 +3678,11 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3702,35 +3702,23 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105144</v>
+        <v>55611</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3745,22 +3733,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C000508049</t>
+          <t>C001762483</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C000508049 - MAMANI ZARATE DANIEL</t>
+          <t>C001762483 - CCAIHUARI ROJAS OLGA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3780,11 +3768,11 @@
         <v>46235</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17614422</t>
+          <t>S17578463</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3794,11 +3782,11 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3807,7 +3795,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3818,14 +3806,26 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
       <c r="AB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>98884</v>
+        <v>48730</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C001392016</t>
+          <t>C001740791</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C001392016 - VELIZ PACHECO NELLY PIEDAD</t>
+          <t>C001740791 - ANYAIPOMA MONTES LEANDRA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3884,11 +3884,11 @@
         <v>46235</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17780287</t>
+          <t>S17740947</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3929,28 +3929,28 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>81123</v>
+        <v>47553</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C001744346</t>
+          <t>C001757239</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C001744346 - SANCHEZ CABALLERO SANDRA JULIANA</t>
+          <t>C001757239 - ESPINOZA SUICA PAMELA ALESSANDRA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4000,11 +4000,11 @@
         <v>46235</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17651959</t>
+          <t>S17530484</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4014,11 +4014,11 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4040,33 +4040,33 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>76636</v>
+        <v>46424</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C004204018</t>
+          <t>C001692252</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C004204018 - DIAZ TANAKA ROXANA CECILIA</t>
+          <t>C001692252 - SALAZAR HUARACHI CRHISTIAN JEFFERSON</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4116,11 +4116,11 @@
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46242</v>
+        <v>46237</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17729235</t>
+          <t>S17569222</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4130,11 +4130,11 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4156,33 +4156,33 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74108</v>
+        <v>38316</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>45461954</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C004094472</t>
+          <t>C001655046</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C004094472 - QUINTANILLA HERRERA BRANDOT ANTHONY</t>
+          <t>C001655046 - TUCNO HUAMANI FAUSTINA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4232,11 +4232,11 @@
         <v>46235</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17791422</t>
+          <t>S17653141</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4246,11 +4246,11 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4277,28 +4277,28 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3300</v>
+        <v>108526</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4313,22 +4313,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C000505145</t>
+          <t>C001670096</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C000505145 - ROJAS CONDO FORTUNATA</t>
+          <t>C001670096 - GROUP ONE SAC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17656685</t>
+          <t>S17661584</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4362,11 +4362,11 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4386,23 +4386,35 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
       <c r="AB34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55611</v>
+        <v>105144</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4417,22 +4429,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C001762483</t>
+          <t>C000508049</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C001762483 - CCAIHUARI ROJAS OLGA</t>
+          <t>C000508049 - MAMANI ZARATE DANIEL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4452,11 +4464,11 @@
         <v>46235</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17578463</t>
+          <t>S17614422</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4466,11 +4478,11 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -4479,7 +4491,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4490,26 +4502,14 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>48730</v>
+        <v>98884</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C001740791</t>
+          <t>C001392016</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C001740791 - ANYAIPOMA MONTES LEANDRA</t>
+          <t>C001392016 - VELIZ PACHECO NELLY PIEDAD</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4568,11 +4568,11 @@
         <v>46235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17740947</t>
+          <t>S17780287</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4613,28 +4613,28 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>47553</v>
+        <v>81123</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ANA ELIZABETH FLORES TAPIA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>41979351</t>
+          <t>10027259</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C001757239</t>
+          <t>C001744346</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C001757239 - ESPINOZA SUICA PAMELA ALESSANDRA</t>
+          <t>C001744346 - SANCHEZ CABALLERO SANDRA JULIANA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4684,11 +4684,11 @@
         <v>46235</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17530484</t>
+          <t>S17651959</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4698,11 +4698,11 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4724,33 +4724,33 @@
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>46424</v>
+        <v>76636</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>ANA ELIZABETH FLORES TAPIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>41979351</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C001692252</t>
+          <t>C004204018</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C001692252 - SALAZAR HUARACHI CRHISTIAN JEFFERSON</t>
+          <t>C004204018 - DIAZ TANAKA ROXANA CECILIA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4800,11 +4800,11 @@
         <v>46235</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17569222</t>
+          <t>S17729235</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4814,11 +4814,11 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>41979351LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4840,33 +4840,33 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38316</v>
+        <v>74108</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>10027259</t>
+          <t>45461954</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C001655046</t>
+          <t>C004094472</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C001655046 - TUCNO HUAMANI FAUSTINA</t>
+          <t>C004094472 - QUINTANILLA HERRERA BRANDOT ANTHONY</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4916,11 +4916,11 @@
         <v>46235</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>S17653141</t>
+          <t>S17791422</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4930,11 +4930,11 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>10027259LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
+          <t>45461954LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000000460</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
